--- a/artfynd/A 19650-2024 artfynd.xlsx
+++ b/artfynd/A 19650-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>119723000</v>
       </c>
       <c r="B2" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 19650-2024 artfynd.xlsx
+++ b/artfynd/A 19650-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -795,6 +795,913 @@
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>120496521</v>
+      </c>
+      <c r="B3" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Mörtsjön, Mörtsjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>516339</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6713673</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Stor mängd bladrosetter.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>120497316</v>
+      </c>
+      <c r="B4" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Mörtsjöklack, Mörtsjöklack, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>516439</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6713453</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>120496014</v>
+      </c>
+      <c r="B5" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Mörtsjön, Mörtsjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>516323</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6713695</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>120497848</v>
+      </c>
+      <c r="B6" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Mörtsjön, Mörtsjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>516359</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6713691</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>120497918</v>
+      </c>
+      <c r="B7" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Mörtsjön, Mörtsjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>516339</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6713724</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>120496652</v>
+      </c>
+      <c r="B8" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Mörtsjön, Mörtsjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>516335</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6713671</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>120497764</v>
+      </c>
+      <c r="B9" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Mörtsjön, Mörtsjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>516341</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6713675</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 19650-2024 artfynd.xlsx
+++ b/artfynd/A 19650-2024 artfynd.xlsx
@@ -797,7 +797,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120496521</v>
+        <v>120497848</v>
       </c>
       <c r="B3" t="n">
         <v>97930</v>
@@ -837,7 +837,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -856,10 +856,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>516339</v>
+        <v>516359</v>
       </c>
       <c r="R3" t="n">
-        <v>6713673</v>
+        <v>6713691</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -901,12 +901,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:38</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Stor mängd bladrosetter.</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -933,7 +928,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120497316</v>
+        <v>120496014</v>
       </c>
       <c r="B4" t="n">
         <v>97930</v>
@@ -968,12 +963,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -983,14 +978,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mörtsjöklack, Mörtsjöklack, Dlr</t>
+          <t>Mörtsjön, Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>516439</v>
+        <v>516323</v>
       </c>
       <c r="R4" t="n">
-        <v>6713453</v>
+        <v>6713695</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1022,7 +1017,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1032,7 +1027,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1059,7 +1054,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120496014</v>
+        <v>120497918</v>
       </c>
       <c r="B5" t="n">
         <v>97930</v>
@@ -1107,16 +1102,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Mörtsjön, Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>516323</v>
+        <v>516339</v>
       </c>
       <c r="R5" t="n">
-        <v>6713695</v>
+        <v>6713724</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1148,7 +1148,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1158,7 +1158,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1185,7 +1185,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120497848</v>
+        <v>120497764</v>
       </c>
       <c r="B6" t="n">
         <v>97930</v>
@@ -1233,21 +1233,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Mörtsjön, Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>516359</v>
+        <v>516341</v>
       </c>
       <c r="R6" t="n">
-        <v>6713691</v>
+        <v>6713675</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1279,7 +1274,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1289,7 +1284,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1316,7 +1311,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120497918</v>
+        <v>120497316</v>
       </c>
       <c r="B7" t="n">
         <v>97930</v>
@@ -1351,12 +1346,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1364,21 +1359,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Mörtsjön, Mörtsjön, Dlr</t>
+          <t>Mörtsjöklack, Mörtsjöklack, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>516339</v>
+        <v>516439</v>
       </c>
       <c r="R7" t="n">
-        <v>6713724</v>
+        <v>6713453</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1410,7 +1400,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1420,7 +1410,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1578,7 +1568,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120497764</v>
+        <v>120496521</v>
       </c>
       <c r="B9" t="n">
         <v>97930</v>
@@ -1618,7 +1608,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1626,16 +1616,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Mörtsjön, Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>516341</v>
+        <v>516339</v>
       </c>
       <c r="R9" t="n">
-        <v>6713675</v>
+        <v>6713673</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1667,7 +1662,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1677,7 +1672,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Stor mängd bladrosetter.</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 19650-2024 artfynd.xlsx
+++ b/artfynd/A 19650-2024 artfynd.xlsx
@@ -928,7 +928,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120496014</v>
+        <v>120497764</v>
       </c>
       <c r="B4" t="n">
         <v>97930</v>
@@ -968,7 +968,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,10 +982,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>516323</v>
+        <v>516341</v>
       </c>
       <c r="R4" t="n">
-        <v>6713695</v>
+        <v>6713675</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1017,7 +1017,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1054,7 +1054,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120497918</v>
+        <v>120496652</v>
       </c>
       <c r="B5" t="n">
         <v>97930</v>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>516339</v>
+        <v>516335</v>
       </c>
       <c r="R5" t="n">
-        <v>6713724</v>
+        <v>6713671</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1148,7 +1148,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1158,7 +1158,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1185,7 +1185,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120497764</v>
+        <v>120496014</v>
       </c>
       <c r="B6" t="n">
         <v>97930</v>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1239,10 +1239,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>516341</v>
+        <v>516323</v>
       </c>
       <c r="R6" t="n">
-        <v>6713675</v>
+        <v>6713695</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1437,7 +1437,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120496652</v>
+        <v>120496521</v>
       </c>
       <c r="B8" t="n">
         <v>97930</v>
@@ -1472,12 +1472,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>516335</v>
+        <v>516339</v>
       </c>
       <c r="R8" t="n">
-        <v>6713671</v>
+        <v>6713673</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1541,7 +1541,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Stor mängd bladrosetter.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1568,7 +1573,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120496521</v>
+        <v>120497918</v>
       </c>
       <c r="B9" t="n">
         <v>97930</v>
@@ -1608,7 +1613,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1630,7 +1635,7 @@
         <v>516339</v>
       </c>
       <c r="R9" t="n">
-        <v>6713673</v>
+        <v>6713724</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1662,7 +1667,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1672,12 +1677,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:38</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Stor mängd bladrosetter.</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 19650-2024 artfynd.xlsx
+++ b/artfynd/A 19650-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1702,6 +1702,269 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>121411948</v>
+      </c>
+      <c r="B10" t="n">
+        <v>98081</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Mörtsjön, Mörtsjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>516331</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6713695</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Överblommad och bladrosetter inom 2 kv/dm precis i kant med tänkt basväg.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>121411488</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57351</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Mörtsjöklack, Mörtsjöklack, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>516442</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6713442</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Svårt att arta, granstam levande men verkar skadad, ca 140cm upp, 45mm ingångshål, ringhack från Tretåig finns bara ca 100m bort.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 19650-2024 artfynd.xlsx
+++ b/artfynd/A 19650-2024 artfynd.xlsx
@@ -1707,7 +1707,7 @@
         <v>121411948</v>
       </c>
       <c r="B10" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 19650-2024 artfynd.xlsx
+++ b/artfynd/A 19650-2024 artfynd.xlsx
@@ -1707,7 +1707,7 @@
         <v>121411948</v>
       </c>
       <c r="B10" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 19650-2024 artfynd.xlsx
+++ b/artfynd/A 19650-2024 artfynd.xlsx
@@ -1707,7 +1707,7 @@
         <v>121411948</v>
       </c>
       <c r="B10" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>121411488</v>
       </c>
       <c r="B11" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 19650-2024 artfynd.xlsx
+++ b/artfynd/A 19650-2024 artfynd.xlsx
@@ -1704,10 +1704,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121411948</v>
+        <v>121411488</v>
       </c>
       <c r="B10" t="n">
-        <v>98098</v>
+        <v>57354</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1716,40 +1716,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1759,14 +1750,14 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Mörtsjön, Mörtsjön, Dlr</t>
+          <t>Mörtsjöklack, Mörtsjöklack, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>516331</v>
+        <v>516442</v>
       </c>
       <c r="R10" t="n">
-        <v>6713695</v>
+        <v>6713442</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1798,7 +1789,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1808,12 +1799,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Överblommad och bladrosetter inom 2 kv/dm precis i kant med tänkt basväg.</t>
+          <t>Svårt att arta, granstam levande men verkar skadad, ca 140cm upp, 45mm ingångshål, ringhack från Tretåig finns bara ca 100m bort.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1840,10 +1831,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121411488</v>
+        <v>121411948</v>
       </c>
       <c r="B11" t="n">
-        <v>57354</v>
+        <v>98098</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1852,31 +1843,40 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1886,14 +1886,14 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Mörtsjöklack, Mörtsjöklack, Dlr</t>
+          <t>Mörtsjön, Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>516442</v>
+        <v>516331</v>
       </c>
       <c r="R11" t="n">
-        <v>6713442</v>
+        <v>6713695</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1925,7 +1925,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Svårt att arta, granstam levande men verkar skadad, ca 140cm upp, 45mm ingångshål, ringhack från Tretåig finns bara ca 100m bort.</t>
+          <t>Överblommad och bladrosetter inom 2 kv/dm precis i kant med tänkt basväg.</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 19650-2024 artfynd.xlsx
+++ b/artfynd/A 19650-2024 artfynd.xlsx
@@ -1704,10 +1704,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121411488</v>
+        <v>121411948</v>
       </c>
       <c r="B10" t="n">
-        <v>57354</v>
+        <v>98104</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1716,31 +1716,40 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1750,14 +1759,14 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Mörtsjöklack, Mörtsjöklack, Dlr</t>
+          <t>Mörtsjön, Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>516442</v>
+        <v>516331</v>
       </c>
       <c r="R10" t="n">
-        <v>6713442</v>
+        <v>6713695</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1789,7 +1798,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1799,12 +1808,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Svårt att arta, granstam levande men verkar skadad, ca 140cm upp, 45mm ingångshål, ringhack från Tretåig finns bara ca 100m bort.</t>
+          <t>Överblommad och bladrosetter inom 2 kv/dm precis i kant med tänkt basväg.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1831,10 +1840,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121411948</v>
+        <v>121411488</v>
       </c>
       <c r="B11" t="n">
-        <v>98098</v>
+        <v>57355</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1843,40 +1852,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1886,14 +1886,14 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Mörtsjön, Mörtsjön, Dlr</t>
+          <t>Mörtsjöklack, Mörtsjöklack, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>516331</v>
+        <v>516442</v>
       </c>
       <c r="R11" t="n">
-        <v>6713695</v>
+        <v>6713442</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1925,7 +1925,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Överblommad och bladrosetter inom 2 kv/dm precis i kant med tänkt basväg.</t>
+          <t>Svårt att arta, granstam levande men verkar skadad, ca 140cm upp, 45mm ingångshål, ringhack från Tretåig finns bara ca 100m bort.</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 19650-2024 artfynd.xlsx
+++ b/artfynd/A 19650-2024 artfynd.xlsx
@@ -1704,10 +1704,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121411948</v>
+        <v>121411488</v>
       </c>
       <c r="B10" t="n">
-        <v>98104</v>
+        <v>57356</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1716,40 +1716,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1759,14 +1750,14 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Mörtsjön, Mörtsjön, Dlr</t>
+          <t>Mörtsjöklack, Mörtsjöklack, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>516331</v>
+        <v>516442</v>
       </c>
       <c r="R10" t="n">
-        <v>6713695</v>
+        <v>6713442</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1798,7 +1789,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1808,12 +1799,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Överblommad och bladrosetter inom 2 kv/dm precis i kant med tänkt basväg.</t>
+          <t>Svårt att arta, granstam levande men verkar skadad, ca 140cm upp, 45mm ingångshål, ringhack från Tretåig finns bara ca 100m bort.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1840,10 +1831,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121411488</v>
+        <v>121411948</v>
       </c>
       <c r="B11" t="n">
-        <v>57355</v>
+        <v>98105</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1852,31 +1843,40 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1886,14 +1886,14 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Mörtsjöklack, Mörtsjöklack, Dlr</t>
+          <t>Mörtsjön, Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>516442</v>
+        <v>516331</v>
       </c>
       <c r="R11" t="n">
-        <v>6713442</v>
+        <v>6713695</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1925,7 +1925,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Svårt att arta, granstam levande men verkar skadad, ca 140cm upp, 45mm ingångshål, ringhack från Tretåig finns bara ca 100m bort.</t>
+          <t>Överblommad och bladrosetter inom 2 kv/dm precis i kant med tänkt basväg.</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 19650-2024 artfynd.xlsx
+++ b/artfynd/A 19650-2024 artfynd.xlsx
@@ -1704,10 +1704,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121411488</v>
+        <v>121411948</v>
       </c>
       <c r="B10" t="n">
-        <v>57356</v>
+        <v>98105</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1716,31 +1716,40 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1750,14 +1759,14 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Mörtsjöklack, Mörtsjöklack, Dlr</t>
+          <t>Mörtsjön, Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>516442</v>
+        <v>516331</v>
       </c>
       <c r="R10" t="n">
-        <v>6713442</v>
+        <v>6713695</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1789,7 +1798,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1799,12 +1808,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Svårt att arta, granstam levande men verkar skadad, ca 140cm upp, 45mm ingångshål, ringhack från Tretåig finns bara ca 100m bort.</t>
+          <t>Överblommad och bladrosetter inom 2 kv/dm precis i kant med tänkt basväg.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1831,10 +1840,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121411948</v>
+        <v>121411488</v>
       </c>
       <c r="B11" t="n">
-        <v>98105</v>
+        <v>57356</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1843,40 +1852,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1886,14 +1886,14 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Mörtsjön, Mörtsjön, Dlr</t>
+          <t>Mörtsjöklack, Mörtsjöklack, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>516331</v>
+        <v>516442</v>
       </c>
       <c r="R11" t="n">
-        <v>6713695</v>
+        <v>6713442</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1925,7 +1925,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Överblommad och bladrosetter inom 2 kv/dm precis i kant med tänkt basväg.</t>
+          <t>Svårt att arta, granstam levande men verkar skadad, ca 140cm upp, 45mm ingångshål, ringhack från Tretåig finns bara ca 100m bort.</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 19650-2024 artfynd.xlsx
+++ b/artfynd/A 19650-2024 artfynd.xlsx
@@ -1704,10 +1704,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121411948</v>
+        <v>121411488</v>
       </c>
       <c r="B10" t="n">
-        <v>98105</v>
+        <v>57356</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1716,40 +1716,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1759,14 +1750,14 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Mörtsjön, Mörtsjön, Dlr</t>
+          <t>Mörtsjöklack, Mörtsjöklack, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>516331</v>
+        <v>516442</v>
       </c>
       <c r="R10" t="n">
-        <v>6713695</v>
+        <v>6713442</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1798,7 +1789,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1808,12 +1799,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Överblommad och bladrosetter inom 2 kv/dm precis i kant med tänkt basväg.</t>
+          <t>Svårt att arta, granstam levande men verkar skadad, ca 140cm upp, 45mm ingångshål, ringhack från Tretåig finns bara ca 100m bort.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1840,10 +1831,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121411488</v>
+        <v>121411948</v>
       </c>
       <c r="B11" t="n">
-        <v>57356</v>
+        <v>98105</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1852,31 +1843,40 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1886,14 +1886,14 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Mörtsjöklack, Mörtsjöklack, Dlr</t>
+          <t>Mörtsjön, Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>516442</v>
+        <v>516331</v>
       </c>
       <c r="R11" t="n">
-        <v>6713442</v>
+        <v>6713695</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1925,7 +1925,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Svårt att arta, granstam levande men verkar skadad, ca 140cm upp, 45mm ingångshål, ringhack från Tretåig finns bara ca 100m bort.</t>
+          <t>Överblommad och bladrosetter inom 2 kv/dm precis i kant med tänkt basväg.</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 19650-2024 artfynd.xlsx
+++ b/artfynd/A 19650-2024 artfynd.xlsx
@@ -1707,7 +1707,7 @@
         <v>121411488</v>
       </c>
       <c r="B10" t="n">
-        <v>57356</v>
+        <v>57357</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>121411948</v>
       </c>
       <c r="B11" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 19650-2024 artfynd.xlsx
+++ b/artfynd/A 19650-2024 artfynd.xlsx
@@ -1707,7 +1707,7 @@
         <v>121411488</v>
       </c>
       <c r="B10" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 19650-2024 artfynd.xlsx
+++ b/artfynd/A 19650-2024 artfynd.xlsx
@@ -1811,7 +1811,7 @@
         <v>0</v>
       </c>
       <c r="AE10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG10" t="b">
         <v>0</v>

--- a/artfynd/A 19650-2024 artfynd.xlsx
+++ b/artfynd/A 19650-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1965,6 +1965,120 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>131618829</v>
+      </c>
+      <c r="B12" t="n">
+        <v>93117</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>788</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Gul taggsvamp</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hydnellum geogenium</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.) Banker</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Mörtsjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>516329</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6713697</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Strax intill bäcken.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 19650-2024 artfynd.xlsx
+++ b/artfynd/A 19650-2024 artfynd.xlsx
@@ -1970,7 +1970,7 @@
         <v>131618829</v>
       </c>
       <c r="B12" t="n">
-        <v>93117</v>
+        <v>93118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 19650-2024 artfynd.xlsx
+++ b/artfynd/A 19650-2024 artfynd.xlsx
@@ -1970,7 +1970,7 @@
         <v>131618829</v>
       </c>
       <c r="B12" t="n">
-        <v>93118</v>
+        <v>93119</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 19650-2024 artfynd.xlsx
+++ b/artfynd/A 19650-2024 artfynd.xlsx
@@ -1970,7 +1970,7 @@
         <v>131618829</v>
       </c>
       <c r="B12" t="n">
-        <v>93119</v>
+        <v>93122</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 19650-2024 artfynd.xlsx
+++ b/artfynd/A 19650-2024 artfynd.xlsx
@@ -1970,7 +1970,7 @@
         <v>131618829</v>
       </c>
       <c r="B12" t="n">
-        <v>93122</v>
+        <v>93128</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 19650-2024 artfynd.xlsx
+++ b/artfynd/A 19650-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119723000</v>
+        <v>131618829</v>
       </c>
       <c r="B2" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93273</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,41 +686,48 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>788</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gul taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum geogenium</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Fr.) Banker</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Amsbergs stenbrott, Dlr</t>
+          <t>Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>516405</v>
+        <v>516329</v>
       </c>
       <c r="R2" t="n">
-        <v>6713635</v>
+        <v>6713697</v>
       </c>
       <c r="S2" t="n">
-        <v>71</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,27 +751,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>13:36</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-06</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>13:36</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Knärot spridd i bestånd främst i svackor och ner mot bäcken. Blandbestånd med tall på åsen och gran ner mot bäck</t>
+          <t>Strax intill bäcken.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,49 +777,44 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Maria  Warg</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Maria  Warg</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120496521</v>
+        <v>121405223</v>
       </c>
       <c r="B3" t="n">
-        <v>98050</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -837,29 +824,19 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Mörtsjön, Mörtsjön, Dlr</t>
+          <t>Mörtsjöklack, Mörtsjöklack, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>516339</v>
+        <v>516397</v>
       </c>
       <c r="R3" t="n">
-        <v>6713673</v>
+        <v>6713446</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -886,27 +863,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2024-11-30</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2024-11-30</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:38</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Stor mängd bladrosetter.</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -933,64 +905,56 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120497316</v>
+        <v>121405198</v>
       </c>
       <c r="B4" t="n">
-        <v>98050</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Mörtsjöklack, Mörtsjöklack, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>516439</v>
+        <v>516393</v>
       </c>
       <c r="R4" t="n">
-        <v>6713453</v>
+        <v>6713452</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1017,22 +981,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2024-11-30</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2024-11-30</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Mycket på granlåga</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1041,6 +1010,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1059,64 +1029,55 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120496014</v>
+        <v>121405139</v>
       </c>
       <c r="B5" t="n">
-        <v>98050</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Mörtsjön, Mörtsjön, Dlr</t>
+          <t>Mörtsjöklack, Mörtsjöklack, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>516323</v>
+        <v>516373</v>
       </c>
       <c r="R5" t="n">
-        <v>6713695</v>
+        <v>6713470</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1143,22 +1104,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2024-11-30</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2024-11-30</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1185,52 +1151,38 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120497918</v>
+        <v>121411488</v>
       </c>
       <c r="B6" t="n">
-        <v>98050</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1240,14 +1192,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Mörtsjön, Mörtsjön, Dlr</t>
+          <t>Mörtsjöklack, Mörtsjöklack, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>516339</v>
+        <v>516442</v>
       </c>
       <c r="R6" t="n">
-        <v>6713724</v>
+        <v>6713442</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1274,29 +1226,34 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2024-12-01</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2024-12-01</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Svårt att arta, granstam levande men verkar skadad, ca 140cm upp, 45mm ingångshål, ringhack från Tretåig finns bara ca 100m bort.</t>
         </is>
       </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG6" t="b">
         <v>0</v>
@@ -1316,52 +1273,43 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120497764</v>
+        <v>121412055</v>
       </c>
       <c r="B7" t="n">
-        <v>98050</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1370,10 +1318,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>516341</v>
+        <v>516299</v>
       </c>
       <c r="R7" t="n">
-        <v>6713675</v>
+        <v>6713706</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1400,22 +1348,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2024-12-01</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2024-12-01</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1442,15 +1395,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120496652</v>
+        <v>119723000</v>
       </c>
       <c r="B8" t="n">
-        <v>98050</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1475,39 +1423,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Mörtsjön, Mörtsjön, Dlr</t>
+          <t>Amsbergs stenbrott, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>516335</v>
+        <v>516405</v>
       </c>
       <c r="R8" t="n">
-        <v>6713671</v>
+        <v>6713635</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>71</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1531,22 +1464,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2024-05-06</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Knärot spridd i bestånd främst i svackor och ner mot bäcken. Blandbestånd med tall på åsen och gran ner mot bäck</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1555,33 +1493,29 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Maria Warg</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Maria Warg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120497848</v>
+        <v>120496014</v>
       </c>
       <c r="B9" t="n">
-        <v>98050</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1613,7 +1547,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1621,21 +1555,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Mörtsjön, Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>516359</v>
+        <v>516323</v>
       </c>
       <c r="R9" t="n">
-        <v>6713691</v>
+        <v>6713695</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1667,7 +1596,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1677,7 +1606,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1704,60 +1633,59 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121411488</v>
+        <v>120496094</v>
       </c>
       <c r="B10" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Mörtsjöklack, Mörtsjöklack, Dlr</t>
+          <t>Mörtsjön, Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>516442</v>
+        <v>516309</v>
       </c>
       <c r="R10" t="n">
-        <v>6713442</v>
+        <v>6713701</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1784,34 +1712,29 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Svårt att arta, granstam levande men verkar skadad, ca 140cm upp, 45mm ingångshål, ringhack från Tretåig finns bara ca 100m bort.</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="b">
         <v>0</v>
@@ -1831,15 +1754,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121411948</v>
+        <v>120496521</v>
       </c>
       <c r="B11" t="n">
-        <v>98113</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1871,12 +1789,12 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1890,10 +1808,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>516331</v>
+        <v>516339</v>
       </c>
       <c r="R11" t="n">
-        <v>6713695</v>
+        <v>6713673</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1920,27 +1838,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-12-01</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Överblommad och bladrosetter inom 2 kv/dm precis i kant med tänkt basväg.</t>
+          <t>Stor mängd bladrosetter.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1967,56 +1885,64 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131618829</v>
+        <v>120496652</v>
       </c>
       <c r="B12" t="n">
-        <v>93174</v>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>788</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gul taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum geogenium</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Banker</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Mörtsjön, Dlr</t>
+          <t>Mörtsjön, Mörtsjön, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>516329</v>
+        <v>516335</v>
       </c>
       <c r="R12" t="n">
-        <v>6713697</v>
+        <v>6713671</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2043,17 +1969,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Strax intill bäcken.</t>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2062,22 +1993,1281 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>120497316</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Mörtsjöklack, Mörtsjöklack, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>516439</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6713453</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>120497764</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Mörtsjön, Mörtsjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>516341</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6713675</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>120497848</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Mörtsjön, Mörtsjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>516359</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6713691</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>120497918</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Mörtsjön, Mörtsjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>516339</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6713724</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>121405090</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Mörtsjöklack, Mörtsjöklack, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>516360</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6713485</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>121405103</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Mörtsjöklack, Mörtsjöklack, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>516368</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6713481</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>121405156</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Mörtsjöklack, Mörtsjöklack, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>516394</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6713448</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>121405273</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Mörtsjöklack, Mörtsjöklack, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>516396</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6713444</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-11-30</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Spridda över större yta.</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>121411854</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Mörtsjön, Mörtsjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>516317</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6713692</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Överblommade och ca 10 bladrosetter precis i yttre gräns där stora enso ska avverka, bas väg går nån meter ifrån knärot.</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>121411948</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Mörtsjön, Mörtsjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>516331</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6713695</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-12-01</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Överblommad och bladrosetter inom 2 kv/dm precis i kant med tänkt basväg.</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 19650-2024 artfynd.xlsx
+++ b/artfynd/A 19650-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AZ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131618829</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -902,6 +912,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121405223</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1026,6 +1041,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121405198</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1148,6 +1168,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121405139</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1270,6 +1295,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121411488</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1392,6 +1422,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121412055</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1509,6 +1544,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119723000</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1630,6 +1670,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120496014</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1751,6 +1796,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120496094</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1882,6 +1932,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120496521</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2008,6 +2063,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120496652</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2129,6 +2189,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120497316</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2250,6 +2315,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120497764</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2376,6 +2446,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120497848</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2502,6 +2577,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120497918</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2623,6 +2703,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121405090</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2749,6 +2834,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121405103</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2875,6 +2965,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121405156</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3006,6 +3101,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121405273</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3137,6 +3237,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121411854</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3268,8 +3373,36 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121411948</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>